--- a/output/upload/S00028_2246_H건강플러스보험_무배당.xlsx
+++ b/output/upload/S00028_2246_H건강플러스보험_무배당.xlsx
@@ -725,17 +725,9 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
+      <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="D7" s="5" t="inlineStr"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="6" t="inlineStr">
@@ -768,16 +760,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -808,16 +792,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>20260201</t>

--- a/output/upload/S00028_2246_H건강플러스보험_무배당.xlsx
+++ b/output/upload/S00028_2246_H건강플러스보험_무배당.xlsx
@@ -725,11 +725,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -760,8 +780,31 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -792,8 +835,31 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2246A01</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>20260201</t>

--- a/output/upload/S00028_2246_H건강플러스보험_무배당.xlsx
+++ b/output/upload/S00028_2246_H건강플러스보험_무배당.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>2246001</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">

--- a/output/upload/S00028_2246_H건강플러스보험_무배당.xlsx
+++ b/output/upload/S00028_2246_H건강플러스보험_무배당.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -889,6 +889,1326 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2246A02</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2246002</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2246A02</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2246002</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>12</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2246A02</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2246002</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2246A03</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2246003</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2246A03</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2246003</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>12</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2246A03</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2246003</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2246A04</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2246004</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2246A04</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2246004</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>12</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2246A04</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2246004</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2246A05</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2246005</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2246A05</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2246005</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>12</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2246A05</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2246005</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2246A06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2246006</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2246A06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2246006</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>12</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2246A06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2246006</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2246A07</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2246007</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2246A07</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2246007</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>12</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2246A07</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2246007</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2246A08</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2246008</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2246A08</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2246008</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>12</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2246A08</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2246008</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2246A09</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2246009</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2246A09</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2246009</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>12</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2246A09</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2246009</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A3:F3"/>

--- a/output/upload/S00028_2246_H건강플러스보험_무배당.xlsx
+++ b/output/upload/S00028_2246_H건강플러스보험_무배당.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -760,11 +760,7 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
+      <c r="I7" s="6" t="n"/>
       <c r="J7" s="6" t="n">
         <v>1</v>
       </c>
@@ -782,22 +778,22 @@
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246002</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -815,13 +811,8 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
       <c r="J8" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -837,22 +828,22 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>2246A01</t>
+          <t>2246A03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2246001</t>
+          <t>2246003</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -870,13 +861,8 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -892,22 +878,22 @@
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>2246A02</t>
+          <t>2246A04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2246002</t>
+          <t>2246004</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -923,11 +909,6 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>99991231</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>M1</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -947,22 +928,22 @@
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>2246A02</t>
+          <t>2246A05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2246002</t>
+          <t>2246005</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -980,13 +961,8 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
       <c r="J11" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1002,22 +978,22 @@
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>2246A02</t>
+          <t>2246A06</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2246002</t>
+          <t>2246006</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(1년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1035,13 +1011,8 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1057,22 +1028,22 @@
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>2246A03</t>
+          <t>2246A07</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2246003</t>
+          <t>2246007</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1088,11 +1059,6 @@
       <c r="H13" t="inlineStr">
         <is>
           <t>99991231</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>M1</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1112,22 +1078,22 @@
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>2246A03</t>
+          <t>2246A08</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2246003</t>
+          <t>2246008</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1145,13 +1111,8 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
       <c r="J14" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1167,22 +1128,22 @@
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>2246A03</t>
+          <t>2246A09</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2246003</t>
+          <t>2246009</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1200,13 +1161,8 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1214,996 +1170,6 @@
         </is>
       </c>
       <c r="L15" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2246A04</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2246004</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>S00028</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2246A04</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2246004</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>S00028</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>12</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2246A04</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2246004</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(3년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>S00028</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2246A05</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2246005</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>S00028</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2246A05</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2246005</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>S00028</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>12</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2246A05</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2246005</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(4년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>S00028</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2246A06</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2246006</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>S00028</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2246A06</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2246006</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>S00028</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
-      <c r="J23" t="n">
-        <v>12</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2246A06</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2246006</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>S00028</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>S00028</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>S00028</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
-      <c r="J26" t="n">
-        <v>12</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2246A07</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2246007</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>S00028</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2246A08</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2246008</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>S00028</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
-        <v>1</v>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2246A08</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2246008</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>S00028</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
-        <v>12</v>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2246A08</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2246008</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 맞춤고지형 일반가입형Ⅱ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>S00028</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2246A09</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2246009</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>S00028</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="J31" t="n">
-        <v>1</v>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2246A09</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2246009</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>S00028</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
-      <c r="J32" t="n">
-        <v>12</v>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2246A09</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2246009</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>한화생명 H건강플러스보험 무배당 보장형계약 일반고지형 일반가입형Ⅰ 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>S00028</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
         </is>
